--- a/dataset_t6_grouped/results2/G4/G4_T3603_W0074F0002T0006Z000C1N10_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3603_W0074F0002T0006Z000C1N10_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>81.06524331631633</v>
+        <v>13.1731020389014</v>
       </c>
       <c r="D2" t="n">
-        <v>56.50832589151556</v>
+        <v>9.182602957371278</v>
       </c>
       <c r="E2" t="n">
-        <v>20.80620753915397</v>
+        <v>3.38100872511252</v>
       </c>
       <c r="F2" t="n">
-        <v>16.18950237716573</v>
+        <v>2.630794136289432</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>74.38805844001917</v>
+        <v>12.08805949650312</v>
       </c>
       <c r="D3" t="n">
-        <v>35.16824641001533</v>
+        <v>5.714840041627491</v>
       </c>
       <c r="E3" t="n">
-        <v>20.80620753915397</v>
+        <v>3.38100872511252</v>
       </c>
       <c r="F3" t="n">
-        <v>16.18950237716573</v>
+        <v>2.630794136289432</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>50.55046708575559</v>
+        <v>8.214450901435283</v>
       </c>
       <c r="D4" t="n">
-        <v>11.5710366384732</v>
+        <v>1.880293453751894</v>
       </c>
       <c r="E4" t="n">
-        <v>20.80620753915397</v>
+        <v>3.38100872511252</v>
       </c>
       <c r="F4" t="n">
-        <v>16.18950237716573</v>
+        <v>2.630794136289432</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>52.88506151240779</v>
+        <v>8.593822495766267</v>
       </c>
       <c r="D5" t="n">
-        <v>10.13862468959296</v>
+        <v>1.647526512058857</v>
       </c>
       <c r="E5" t="n">
-        <v>20.80620753915397</v>
+        <v>3.38100872511252</v>
       </c>
       <c r="F5" t="n">
-        <v>16.18950237716573</v>
+        <v>2.630794136289432</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>33.99490591527193</v>
+        <v>5.524172211231688</v>
       </c>
       <c r="D6" t="n">
-        <v>20.827453155774</v>
+        <v>3.384461137813275</v>
       </c>
       <c r="E6" t="n">
-        <v>20.80620753915397</v>
+        <v>3.38100872511252</v>
       </c>
       <c r="F6" t="n">
-        <v>16.18950237716573</v>
+        <v>2.630794136289432</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>6.787777987908712</v>
+        <v>1.103013923035166</v>
       </c>
       <c r="D7" t="n">
-        <v>12.56869280839693</v>
+        <v>2.042412581364501</v>
       </c>
       <c r="E7" t="n">
-        <v>20.80620753915397</v>
+        <v>3.38100872511252</v>
       </c>
       <c r="F7" t="n">
-        <v>16.18950237716573</v>
+        <v>2.630794136289432</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>37.59416568191912</v>
+        <v>6.109051923311856</v>
       </c>
       <c r="D8" t="n">
-        <v>30.95479067307349</v>
+        <v>5.030153484374441</v>
       </c>
       <c r="E8" t="n">
-        <v>20.80620753915397</v>
+        <v>3.38100872511252</v>
       </c>
       <c r="F8" t="n">
-        <v>16.18950237716573</v>
+        <v>2.630794136289432</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>29.39153161910254</v>
+        <v>4.776123888104164</v>
       </c>
       <c r="D9" t="n">
-        <v>60.67962934563429</v>
+        <v>9.860439768665572</v>
       </c>
       <c r="E9" t="n">
-        <v>20.80620753915397</v>
+        <v>3.38100872511252</v>
       </c>
       <c r="F9" t="n">
-        <v>16.18950237716573</v>
+        <v>2.630794136289432</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>32.17733986910535</v>
+        <v>5.22881772872962</v>
       </c>
       <c r="D10" t="n">
-        <v>36.68538498429899</v>
+        <v>5.961375059948586</v>
       </c>
       <c r="E10" t="n">
-        <v>20.80620753915397</v>
+        <v>3.38100872511252</v>
       </c>
       <c r="F10" t="n">
-        <v>16.18950237716573</v>
+        <v>2.630794136289432</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>6.598232365660904</v>
+        <v>1.072212759419897</v>
       </c>
       <c r="D11" t="n">
-        <v>3.523928724451497</v>
+        <v>0.5726384177233683</v>
       </c>
       <c r="E11" t="n">
-        <v>20.80620753915397</v>
+        <v>3.38100872511252</v>
       </c>
       <c r="F11" t="n">
-        <v>16.18950237716573</v>
+        <v>2.630794136289432</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>25.55273153478682</v>
+        <v>4.152318874402858</v>
       </c>
       <c r="D12" t="n">
-        <v>29.15154369840472</v>
+        <v>4.737125850990767</v>
       </c>
       <c r="E12" t="n">
-        <v>20.80620753915397</v>
+        <v>3.38100872511252</v>
       </c>
       <c r="F12" t="n">
-        <v>16.18950237716573</v>
+        <v>2.630794136289432</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>35.40423116655163</v>
+        <v>5.753187564564641</v>
       </c>
       <c r="D13" t="n">
-        <v>40.06783373923177</v>
+        <v>6.511022982625162</v>
       </c>
       <c r="E13" t="n">
-        <v>20.80620753915397</v>
+        <v>3.38100872511252</v>
       </c>
       <c r="F13" t="n">
-        <v>16.18950237716573</v>
+        <v>2.630794136289432</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>23.36175413595767</v>
+        <v>3.796285047093122</v>
       </c>
       <c r="D14" t="n">
-        <v>24.60481701091278</v>
+        <v>3.998282764273326</v>
       </c>
       <c r="E14" t="n">
-        <v>20.80620753915397</v>
+        <v>3.38100872511252</v>
       </c>
       <c r="F14" t="n">
-        <v>16.18950237716573</v>
+        <v>2.630794136289432</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>30.80992385875126</v>
+        <v>5.006612627047081</v>
       </c>
       <c r="D15" t="n">
-        <v>33.58181214350577</v>
+        <v>5.457044473319688</v>
       </c>
       <c r="E15" t="n">
-        <v>20.80620753915397</v>
+        <v>3.38100872511252</v>
       </c>
       <c r="F15" t="n">
-        <v>16.18950237716573</v>
+        <v>2.630794136289432</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
